--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/168.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/168.xlsx
@@ -426,13 +426,13 @@
         <v>-14.58260629807677</v>
       </c>
       <c r="E2">
-        <v>-6.065317893783072</v>
+        <v>-7.268723633529408</v>
       </c>
       <c r="F2">
-        <v>-5.811763717733629</v>
+        <v>-5.08637066677613</v>
       </c>
       <c r="G2">
-        <v>-1.584275960668718</v>
+        <v>-4.905315929299395</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.55826508983346</v>
       </c>
       <c r="E3">
-        <v>-6.694748610005205</v>
+        <v>-8.102841374898242</v>
       </c>
       <c r="F3">
-        <v>-5.243794436371551</v>
+        <v>-5.091583582841947</v>
       </c>
       <c r="G3">
-        <v>-2.485664679010398</v>
+        <v>-5.338030715646452</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.38721326450111</v>
       </c>
       <c r="E4">
-        <v>-6.580042363390915</v>
+        <v>-8.659825563945665</v>
       </c>
       <c r="F4">
-        <v>-5.175271056444573</v>
+        <v>-4.767167571781369</v>
       </c>
       <c r="G4">
-        <v>-2.606827335202184</v>
+        <v>-4.965667174480308</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.08313901028476</v>
       </c>
       <c r="E5">
-        <v>-9.142696747383555</v>
+        <v>-9.946790706081535</v>
       </c>
       <c r="F5">
-        <v>-5.106873588362821</v>
+        <v>-4.425543056295033</v>
       </c>
       <c r="G5">
-        <v>-3.073607635148343</v>
+        <v>-3.861524094585964</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.67269420501497</v>
       </c>
       <c r="E6">
-        <v>-10.57131255647935</v>
+        <v>-11.02743857242794</v>
       </c>
       <c r="F6">
-        <v>-5.560604377939625</v>
+        <v>-4.669630623571338</v>
       </c>
       <c r="G6">
-        <v>-2.2557208069437</v>
+        <v>-5.592704362891507</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.16655690796894</v>
       </c>
       <c r="E7">
-        <v>-9.195815747493528</v>
+        <v>-12.14557767508385</v>
       </c>
       <c r="F7">
-        <v>-5.31579198918587</v>
+        <v>-4.925637569406526</v>
       </c>
       <c r="G7">
-        <v>-2.69755945679699</v>
+        <v>-5.339070226945783</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.59231076009008</v>
       </c>
       <c r="E8">
-        <v>-11.3021222203112</v>
+        <v>-13.11132909890765</v>
       </c>
       <c r="F8">
-        <v>-4.780747826982863</v>
+        <v>-4.641976406196279</v>
       </c>
       <c r="G8">
-        <v>-2.125904384712259</v>
+        <v>-5.31274145827196</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.97074114164997</v>
       </c>
       <c r="E9">
-        <v>-13.81261311220949</v>
+        <v>-13.61183416013141</v>
       </c>
       <c r="F9">
-        <v>-5.439198023017926</v>
+        <v>-4.73640034970659</v>
       </c>
       <c r="G9">
-        <v>-1.911308201765622</v>
+        <v>-4.598286004350767</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.30888955082776</v>
       </c>
       <c r="E10">
-        <v>-13.31832564579826</v>
+        <v>-15.50396192628231</v>
       </c>
       <c r="F10">
-        <v>-4.608844195186507</v>
+        <v>-4.566041623116455</v>
       </c>
       <c r="G10">
-        <v>-2.084049157459253</v>
+        <v>-3.773168944688355</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.6354203622992</v>
       </c>
       <c r="E11">
-        <v>-14.15717564250511</v>
+        <v>-16.83718543040653</v>
       </c>
       <c r="F11">
-        <v>-5.353075977618473</v>
+        <v>-4.673687138742848</v>
       </c>
       <c r="G11">
-        <v>-1.386295405783683</v>
+        <v>-3.82847160792188</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.962598565792304</v>
       </c>
       <c r="E12">
-        <v>-15.32486983622696</v>
+        <v>-16.05749994660989</v>
       </c>
       <c r="F12">
-        <v>-4.688293741156411</v>
+        <v>-4.553930891687526</v>
       </c>
       <c r="G12">
-        <v>-0.7273180740095959</v>
+        <v>-3.416172955915508</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.302118252834708</v>
       </c>
       <c r="E13">
-        <v>-15.19925449572819</v>
+        <v>-17.96851597784678</v>
       </c>
       <c r="F13">
-        <v>-4.68116232618571</v>
+        <v>-4.58343899531005</v>
       </c>
       <c r="G13">
-        <v>-0.5927642611114577</v>
+        <v>-2.697635599344393</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.687937989056191</v>
       </c>
       <c r="E14">
-        <v>-17.46302959521459</v>
+        <v>-18.92133407990467</v>
       </c>
       <c r="F14">
-        <v>-5.049631744094569</v>
+        <v>-4.635312190440757</v>
       </c>
       <c r="G14">
-        <v>-0.04683874895794267</v>
+        <v>-1.521243173600994</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.128603020644221</v>
       </c>
       <c r="E15">
-        <v>-19.12082694536457</v>
+        <v>-20.22679350988787</v>
       </c>
       <c r="F15">
-        <v>-4.888273229335851</v>
+        <v>-4.851493716651553</v>
       </c>
       <c r="G15">
-        <v>-0.4072081836353078</v>
+        <v>-0.5383984822655463</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.642995359483931</v>
       </c>
       <c r="E16">
-        <v>-19.85938029974954</v>
+        <v>-20.54870461319712</v>
       </c>
       <c r="F16">
-        <v>-4.892846645766707</v>
+        <v>-4.59300829554719</v>
       </c>
       <c r="G16">
-        <v>2.079918605835114</v>
+        <v>-0.4743195628074132</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.24811270642335</v>
       </c>
       <c r="E17">
-        <v>-19.31263951890747</v>
+        <v>-22.1309851307952</v>
       </c>
       <c r="F17">
-        <v>-4.58031439346669</v>
+        <v>-4.254655002934509</v>
       </c>
       <c r="G17">
-        <v>2.69161472621733</v>
+        <v>0.2332036087545463</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.936762253616167</v>
       </c>
       <c r="E18">
-        <v>-20.7974219911204</v>
+        <v>-22.87853656303341</v>
       </c>
       <c r="F18">
-        <v>-4.678174404963812</v>
+        <v>-4.144776208790169</v>
       </c>
       <c r="G18">
-        <v>3.110928424221418</v>
+        <v>0.591835007023794</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.71157459386471</v>
       </c>
       <c r="E19">
-        <v>-21.54329788797577</v>
+        <v>-23.8863801527585</v>
       </c>
       <c r="F19">
-        <v>-4.914828203167395</v>
+        <v>-4.378603617415399</v>
       </c>
       <c r="G19">
-        <v>3.244945928742195</v>
+        <v>1.660105015454596</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.559414703254847</v>
       </c>
       <c r="E20">
-        <v>-21.17165961158829</v>
+        <v>-24.3209642178526</v>
       </c>
       <c r="F20">
-        <v>-4.268274191403935</v>
+        <v>-3.86297555876661</v>
       </c>
       <c r="G20">
-        <v>3.923587901019552</v>
+        <v>2.108435645110396</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.456879743359207</v>
       </c>
       <c r="E21">
-        <v>-23.17014764675734</v>
+        <v>-24.75190286137052</v>
       </c>
       <c r="F21">
-        <v>-4.547409983492688</v>
+        <v>-4.092448239955324</v>
       </c>
       <c r="G21">
-        <v>3.207334820870535</v>
+        <v>2.622970564460542</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.396879263942042</v>
       </c>
       <c r="E22">
-        <v>-22.81008414993346</v>
+        <v>-25.78120236094396</v>
       </c>
       <c r="F22">
-        <v>-3.941885837557291</v>
+        <v>-3.973166647421806</v>
       </c>
       <c r="G22">
-        <v>4.815236994384697</v>
+        <v>2.111676669193343</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.356399674350135</v>
       </c>
       <c r="E23">
-        <v>-24.7483480092745</v>
+        <v>-26.75629602664558</v>
       </c>
       <c r="F23">
-        <v>-4.025236993994381</v>
+        <v>-3.807638131157395</v>
       </c>
       <c r="G23">
-        <v>4.525213341871305</v>
+        <v>3.40672235760976</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.32162846938912</v>
       </c>
       <c r="E24">
-        <v>-24.69542826202087</v>
+        <v>-26.40921113632768</v>
       </c>
       <c r="F24">
-        <v>-3.750570244043731</v>
+        <v>-3.545415944699003</v>
       </c>
       <c r="G24">
-        <v>3.748691780179855</v>
+        <v>2.944229214136957</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.290870044788238</v>
       </c>
       <c r="E25">
-        <v>-24.48926042587366</v>
+        <v>-26.71332080831279</v>
       </c>
       <c r="F25">
-        <v>-3.249955516203281</v>
+        <v>-3.692685586670907</v>
       </c>
       <c r="G25">
-        <v>3.144835031634634</v>
+        <v>2.952631378715627</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.251265134838685</v>
       </c>
       <c r="E26">
-        <v>-24.55827436975056</v>
+        <v>-27.11235182397267</v>
       </c>
       <c r="F26">
-        <v>-3.523653904660057</v>
+        <v>-3.820056186892762</v>
       </c>
       <c r="G26">
-        <v>3.947516524177404</v>
+        <v>2.927736076260308</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.207085220667889</v>
       </c>
       <c r="E27">
-        <v>-24.01954898790206</v>
+        <v>-26.53925079593195</v>
       </c>
       <c r="F27">
-        <v>-3.715830171905126</v>
+        <v>-3.891256850265588</v>
       </c>
       <c r="G27">
-        <v>3.867871419593618</v>
+        <v>3.315437374909896</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.163588844183548</v>
       </c>
       <c r="E28">
-        <v>-25.48389898539239</v>
+        <v>-27.26417344355383</v>
       </c>
       <c r="F28">
-        <v>-2.873764057365525</v>
+        <v>-3.52026091177819</v>
       </c>
       <c r="G28">
-        <v>3.062826197535808</v>
+        <v>2.800485326821802</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.121794576632575</v>
       </c>
       <c r="E29">
-        <v>-24.31995436814889</v>
+        <v>-26.95434883737104</v>
       </c>
       <c r="F29">
-        <v>-3.718455268204597</v>
+        <v>-3.549462519461679</v>
       </c>
       <c r="G29">
-        <v>4.201379087765337</v>
+        <v>2.430886091180949</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.098187191641419</v>
       </c>
       <c r="E30">
-        <v>-24.62531389896011</v>
+        <v>-25.12426116512523</v>
       </c>
       <c r="F30">
-        <v>-3.617325690568625</v>
+        <v>-3.470025399002817</v>
       </c>
       <c r="G30">
-        <v>3.279858941999349</v>
+        <v>3.469546580308509</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.098798373336241</v>
       </c>
       <c r="E31">
-        <v>-25.08730428874863</v>
+        <v>-25.99018690792394</v>
       </c>
       <c r="F31">
-        <v>-3.313332249456665</v>
+        <v>-3.499350433429322</v>
       </c>
       <c r="G31">
-        <v>2.906432715715098</v>
+        <v>2.58205222159515</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.130202524643075</v>
       </c>
       <c r="E32">
-        <v>-25.02070402151782</v>
+        <v>-25.23106975307014</v>
       </c>
       <c r="F32">
-        <v>-3.488811114963504</v>
+        <v>-3.578901040222367</v>
       </c>
       <c r="G32">
-        <v>4.432729941686225</v>
+        <v>2.19613199644569</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.207621261065712</v>
       </c>
       <c r="E33">
-        <v>-21.80833588622269</v>
+        <v>-25.09474910001724</v>
       </c>
       <c r="F33">
-        <v>-3.029636294815502</v>
+        <v>-3.868185161362816</v>
       </c>
       <c r="G33">
-        <v>3.042943061026945</v>
+        <v>1.94025662116988</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.326331393162556</v>
       </c>
       <c r="E34">
-        <v>-24.07245514973367</v>
+        <v>-25.23737791736283</v>
       </c>
       <c r="F34">
-        <v>-3.870308267016191</v>
+        <v>-3.945972173955301</v>
       </c>
       <c r="G34">
-        <v>3.651563684603178</v>
+        <v>2.526123865254702</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.490587139538697</v>
       </c>
       <c r="E35">
-        <v>-21.19157131180001</v>
+        <v>-24.02017391731512</v>
       </c>
       <c r="F35">
-        <v>-3.280912434413301</v>
+        <v>-3.547414795241958</v>
       </c>
       <c r="G35">
-        <v>3.574004223709133</v>
+        <v>2.072721479832738</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.700867575196394</v>
       </c>
       <c r="E36">
-        <v>-21.18780362142563</v>
+        <v>-23.75540762750866</v>
       </c>
       <c r="F36">
-        <v>-3.150604443381119</v>
+        <v>-3.554745018389331</v>
       </c>
       <c r="G36">
-        <v>2.616819570848576</v>
+        <v>1.381112100678056</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.942855788737409</v>
       </c>
       <c r="E37">
-        <v>-21.83240472557346</v>
+        <v>-22.88671951556527</v>
       </c>
       <c r="F37">
-        <v>-3.174651120716986</v>
+        <v>-3.585142788602462</v>
       </c>
       <c r="G37">
-        <v>2.129729074018988</v>
+        <v>1.521446126087761</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.215312913489957</v>
       </c>
       <c r="E38">
-        <v>-21.40306916185425</v>
+        <v>-21.29247476963893</v>
       </c>
       <c r="F38">
-        <v>-3.038232263354352</v>
+        <v>-3.653773856291803</v>
       </c>
       <c r="G38">
-        <v>3.773431486994829</v>
+        <v>1.373352181934004</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.507836652554048</v>
       </c>
       <c r="E39">
-        <v>-19.47517550799077</v>
+        <v>-20.229234357378</v>
       </c>
       <c r="F39">
-        <v>-3.178097129112632</v>
+        <v>-3.403447025737612</v>
       </c>
       <c r="G39">
-        <v>2.369266907058494</v>
+        <v>1.060376517196845</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.80579129131698</v>
       </c>
       <c r="E40">
-        <v>-18.82088799794053</v>
+        <v>-20.85702123753535</v>
       </c>
       <c r="F40">
-        <v>-3.106706769604565</v>
+        <v>-3.464534151489659</v>
       </c>
       <c r="G40">
-        <v>1.807599750865745</v>
+        <v>0.2132443296982803</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.108369849682383</v>
       </c>
       <c r="E41">
-        <v>-18.68497943602233</v>
+        <v>-20.15822335646372</v>
       </c>
       <c r="F41">
-        <v>-2.849968375352706</v>
+        <v>-3.283124175378776</v>
       </c>
       <c r="G41">
-        <v>1.49942106661499</v>
+        <v>-0.1847726288516767</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.400238599294573</v>
       </c>
       <c r="E42">
-        <v>-17.33118760295527</v>
+        <v>-18.41041352846327</v>
       </c>
       <c r="F42">
-        <v>-3.111314977466339</v>
+        <v>-3.643941135220573</v>
       </c>
       <c r="G42">
-        <v>1.857622093964132</v>
+        <v>0.5128487010023227</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.674447543965885</v>
       </c>
       <c r="E43">
-        <v>-17.15291516669531</v>
+        <v>-17.27804143200125</v>
       </c>
       <c r="F43">
-        <v>-2.747164667195676</v>
+        <v>-3.289623546021141</v>
       </c>
       <c r="G43">
-        <v>0.7281963777863742</v>
+        <v>0.1553726831262807</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.93365233544379</v>
       </c>
       <c r="E44">
-        <v>-15.9355300276873</v>
+        <v>-16.9154510466811</v>
       </c>
       <c r="F44">
-        <v>-2.675654194414203</v>
+        <v>-2.952285831844292</v>
       </c>
       <c r="G44">
-        <v>0.4422976650149145</v>
+        <v>-1.474965057507522</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.164611870997676</v>
       </c>
       <c r="E45">
-        <v>-14.63314543155531</v>
+        <v>-15.66244493112874</v>
       </c>
       <c r="F45">
-        <v>-2.72742053014995</v>
+        <v>-2.811146108653104</v>
       </c>
       <c r="G45">
-        <v>0.8457571604314333</v>
+        <v>-1.494695908921579</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.372004438945977</v>
       </c>
       <c r="E46">
-        <v>-14.81278546696559</v>
+        <v>-14.65479153731198</v>
       </c>
       <c r="F46">
-        <v>-2.96818965761064</v>
+        <v>-2.864150853656036</v>
       </c>
       <c r="G46">
-        <v>-0.5430663514759188</v>
+        <v>-0.9965812954462179</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.558884355097208</v>
       </c>
       <c r="E47">
-        <v>-13.29648028718526</v>
+        <v>-14.39156492866812</v>
       </c>
       <c r="F47">
-        <v>-2.487196468440302</v>
+        <v>-2.970046028960314</v>
       </c>
       <c r="G47">
-        <v>-1.230484579977884</v>
+        <v>-2.22337677702502</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.719184292905229</v>
       </c>
       <c r="E48">
-        <v>-10.77039333080456</v>
+        <v>-13.56676225833306</v>
       </c>
       <c r="F48">
-        <v>-2.509535052191596</v>
+        <v>-2.923155463757445</v>
       </c>
       <c r="G48">
-        <v>-0.1834914477279787</v>
+        <v>-2.141414290563744</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.863988650246847</v>
       </c>
       <c r="E49">
-        <v>-10.72915704649071</v>
+        <v>-12.99288233276302</v>
       </c>
       <c r="F49">
-        <v>-2.268642497987889</v>
+        <v>-2.384694286017891</v>
       </c>
       <c r="G49">
-        <v>-0.5706233325448121</v>
+        <v>-1.978929404950775</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.993375349735686</v>
       </c>
       <c r="E50">
-        <v>-10.87057676127625</v>
+        <v>-12.65898888722947</v>
       </c>
       <c r="F50">
-        <v>-2.484313749878559</v>
+        <v>-2.805908341565203</v>
       </c>
       <c r="G50">
-        <v>-0.4758722086653314</v>
+        <v>-2.492169900995066</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.10561224252372</v>
       </c>
       <c r="E51">
-        <v>-8.586935246318204</v>
+        <v>-10.31079397529209</v>
       </c>
       <c r="F51">
-        <v>-2.465132074299334</v>
+        <v>-2.385014035835372</v>
       </c>
       <c r="G51">
-        <v>-2.216467668484561</v>
+        <v>-3.640667670024565</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.21305124511523</v>
       </c>
       <c r="E52">
-        <v>-9.795213624096792</v>
+        <v>-9.934686095059032</v>
       </c>
       <c r="F52">
-        <v>-1.940559304435116</v>
+        <v>-2.036447801513576</v>
       </c>
       <c r="G52">
-        <v>-2.629488019418495</v>
+        <v>-3.649612764071676</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.3075469370562</v>
       </c>
       <c r="E53">
-        <v>-8.716250350081237</v>
+        <v>-9.612566681945424</v>
       </c>
       <c r="F53">
-        <v>-2.296879057647115</v>
+        <v>-2.567822296122181</v>
       </c>
       <c r="G53">
-        <v>-2.169355294915193</v>
+        <v>-4.083585557723658</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.39003621118377</v>
       </c>
       <c r="E54">
-        <v>-7.481118121437163</v>
+        <v>-9.622900659630927</v>
       </c>
       <c r="F54">
-        <v>-2.324612798292843</v>
+        <v>-2.315354964199155</v>
       </c>
       <c r="G54">
-        <v>-2.347492439837836</v>
+        <v>-5.340877784810226</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.46752890937645</v>
       </c>
       <c r="E55">
-        <v>-6.232676707684545</v>
+        <v>-9.791790097746993</v>
       </c>
       <c r="F55">
-        <v>-1.898044175853835</v>
+        <v>-2.168899607384203</v>
       </c>
       <c r="G55">
-        <v>-2.640541930974122</v>
+        <v>-4.157851025806128</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.52770616701852</v>
       </c>
       <c r="E56">
-        <v>-6.834470147037867</v>
+        <v>-8.612412441085356</v>
       </c>
       <c r="F56">
-        <v>-2.313670893269264</v>
+        <v>-2.434488278967572</v>
       </c>
       <c r="G56">
-        <v>-3.242730164567551</v>
+        <v>-4.898353852030307</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.57569934098035</v>
       </c>
       <c r="E57">
-        <v>-4.451795434006077</v>
+        <v>-7.93979366825207</v>
       </c>
       <c r="F57">
-        <v>-2.538694413137542</v>
+        <v>-2.349292348324449</v>
       </c>
       <c r="G57">
-        <v>-3.265347811691851</v>
+        <v>-4.884810410229148</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.61188991424605</v>
       </c>
       <c r="E58">
-        <v>-5.874986131240687</v>
+        <v>-6.390480441429834</v>
       </c>
       <c r="F58">
-        <v>-2.116597317938845</v>
+        <v>-2.308552411087366</v>
       </c>
       <c r="G58">
-        <v>-4.32700003958965</v>
+        <v>-5.416904463119589</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.62531107358673</v>
       </c>
       <c r="E59">
-        <v>-3.713753797183978</v>
+        <v>-6.887734058316085</v>
       </c>
       <c r="F59">
-        <v>-2.034981591210621</v>
+        <v>-2.681308630305713</v>
       </c>
       <c r="G59">
-        <v>-3.568570609270317</v>
+        <v>-5.821525960020391</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.62308643077013</v>
       </c>
       <c r="E60">
-        <v>-3.917344931620822</v>
+        <v>-6.657750977362539</v>
       </c>
       <c r="F60">
-        <v>-2.335994566407308</v>
+        <v>-2.227265546218053</v>
       </c>
       <c r="G60">
-        <v>-3.171070095824486</v>
+        <v>-5.752199825882514</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.59939121479816</v>
       </c>
       <c r="E61">
-        <v>-5.512010825629877</v>
+        <v>-6.520108009899398</v>
       </c>
       <c r="F61">
-        <v>-2.177961118403427</v>
+        <v>-2.439251391533669</v>
       </c>
       <c r="G61">
-        <v>-3.5571128111589</v>
+        <v>-5.873236681343807</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.54790926419493</v>
       </c>
       <c r="E62">
-        <v>-1.53580233709095</v>
+        <v>-5.740408940680739</v>
       </c>
       <c r="F62">
-        <v>-2.50405623018948</v>
+        <v>-2.153731371871541</v>
       </c>
       <c r="G62">
-        <v>-4.378287011084039</v>
+        <v>-5.408469193085526</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.47908196175336</v>
       </c>
       <c r="E63">
-        <v>-4.316326134066618</v>
+        <v>-5.673079589134696</v>
       </c>
       <c r="F63">
-        <v>-2.995292182295434</v>
+        <v>-2.106933583817786</v>
       </c>
       <c r="G63">
-        <v>-4.997832434939867</v>
+        <v>-5.857223572570353</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.38356406192205</v>
       </c>
       <c r="E64">
-        <v>-2.570984324400348</v>
+        <v>-4.51327399713421</v>
       </c>
       <c r="F64">
-        <v>-2.505977214196572</v>
+        <v>-2.447768665169254</v>
       </c>
       <c r="G64">
-        <v>-4.620622255104229</v>
+        <v>-5.928807498766013</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.2633335853529</v>
       </c>
       <c r="E65">
-        <v>-2.657383079992691</v>
+        <v>-4.814965463999217</v>
       </c>
       <c r="F65">
-        <v>-2.65367677885053</v>
+        <v>-2.170532319535121</v>
       </c>
       <c r="G65">
-        <v>-4.680175658810179</v>
+        <v>-6.273028092302814</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.12553765988541</v>
       </c>
       <c r="E66">
-        <v>-1.570771213378181</v>
+        <v>-4.444097028193037</v>
       </c>
       <c r="F66">
-        <v>-2.484279786815045</v>
+        <v>-2.214791161499296</v>
       </c>
       <c r="G66">
-        <v>-3.989403847676931</v>
+        <v>-5.828385410377762</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.960408077164866</v>
       </c>
       <c r="E67">
-        <v>-2.391525427950379</v>
+        <v>-4.668297247838789</v>
       </c>
       <c r="F67">
-        <v>-2.704710837802201</v>
+        <v>-2.658916202673236</v>
       </c>
       <c r="G67">
-        <v>-3.466347584108702</v>
+        <v>-5.827719990724368</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.772245967493939</v>
       </c>
       <c r="E68">
-        <v>-1.179031040870649</v>
+        <v>-4.843997510862391</v>
       </c>
       <c r="F68">
-        <v>-2.650417153120514</v>
+        <v>-2.325947298178753</v>
       </c>
       <c r="G68">
-        <v>-2.834745153398848</v>
+        <v>-5.443322616522972</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.560351165030225</v>
       </c>
       <c r="E69">
-        <v>-0.8177403275906922</v>
+        <v>-4.608304024185172</v>
       </c>
       <c r="F69">
-        <v>-2.553887499672287</v>
+        <v>-2.228165153217494</v>
       </c>
       <c r="G69">
-        <v>-3.978436010305326</v>
+        <v>-5.732045224639431</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.314059558766914</v>
       </c>
       <c r="E70">
-        <v>-2.510832604156462</v>
+        <v>-3.379969035026611</v>
       </c>
       <c r="F70">
-        <v>-2.43782245776384</v>
+        <v>-2.359332161246379</v>
       </c>
       <c r="G70">
-        <v>-4.456402643628682</v>
+        <v>-5.663043523964402</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.037614196274369</v>
       </c>
       <c r="E71">
-        <v>-2.64373878780758</v>
+        <v>-4.067074396210434</v>
       </c>
       <c r="F71">
-        <v>-2.320616753941738</v>
+        <v>-2.605418579065639</v>
       </c>
       <c r="G71">
-        <v>-3.509977263770756</v>
+        <v>-4.912956668404032</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.724440211367309</v>
       </c>
       <c r="E72">
-        <v>-2.926021215075711</v>
+        <v>-4.741943820625532</v>
       </c>
       <c r="F72">
-        <v>-2.653134198201696</v>
+        <v>-2.491024354208638</v>
       </c>
       <c r="G72">
-        <v>-3.061136810101908</v>
+        <v>-4.92132572752731</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.366164246838958</v>
       </c>
       <c r="E73">
-        <v>-3.83696904645868</v>
+        <v>-4.537818326255783</v>
       </c>
       <c r="F73">
-        <v>-3.16948873506274</v>
+        <v>-2.32915390839499</v>
       </c>
       <c r="G73">
-        <v>-2.691732896647872</v>
+        <v>-4.313254654510596</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.971543391374436</v>
       </c>
       <c r="E74">
-        <v>-2.244445120655254</v>
+        <v>-4.724468439429932</v>
       </c>
       <c r="F74">
-        <v>-2.946171652044229</v>
+        <v>-2.308781040490539</v>
       </c>
       <c r="G74">
-        <v>-2.832795242076217</v>
+        <v>-4.118816383352581</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.535345378451725</v>
       </c>
       <c r="E75">
-        <v>-4.189266210359404</v>
+        <v>-4.99587347213164</v>
       </c>
       <c r="F75">
-        <v>-3.147079740082208</v>
+        <v>-1.994752756661066</v>
       </c>
       <c r="G75">
-        <v>-3.021022929802559</v>
+        <v>-3.787586370511881</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.061213049468037</v>
       </c>
       <c r="E76">
-        <v>-2.363186237610378</v>
+        <v>-6.382605425130495</v>
       </c>
       <c r="F76">
-        <v>-2.642778777299299</v>
+        <v>-2.251791019912738</v>
       </c>
       <c r="G76">
-        <v>-1.276623653158707</v>
+        <v>-3.554398163816697</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.561729094196336</v>
       </c>
       <c r="E77">
-        <v>-5.559935666053052</v>
+        <v>-5.359048030598787</v>
       </c>
       <c r="F77">
-        <v>-2.873725124097593</v>
+        <v>-2.622101070190618</v>
       </c>
       <c r="G77">
-        <v>-2.17300020555393</v>
+        <v>-3.199640103828397</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.040162291845683</v>
       </c>
       <c r="E78">
-        <v>-4.816532316005871</v>
+        <v>-7.495758677903961</v>
       </c>
       <c r="F78">
-        <v>-3.155644230659751</v>
+        <v>-3.005801679534752</v>
       </c>
       <c r="G78">
-        <v>-1.215835415966609</v>
+        <v>-2.962446137030695</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.51346529350917</v>
       </c>
       <c r="E79">
-        <v>-4.757508185789895</v>
+        <v>-6.931768939566672</v>
       </c>
       <c r="F79">
-        <v>-3.073598581249474</v>
+        <v>-3.010404917192109</v>
       </c>
       <c r="G79">
-        <v>-0.4197551512291455</v>
+        <v>-3.147641365043064</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.99734501425755</v>
       </c>
       <c r="E80">
-        <v>-5.155746718498435</v>
+        <v>-7.677364071033566</v>
       </c>
       <c r="F80">
-        <v>-3.169935225092849</v>
+        <v>-2.540288192020528</v>
       </c>
       <c r="G80">
-        <v>0.6560529693945765</v>
+        <v>-2.147843370001009</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.500948889275945</v>
       </c>
       <c r="E81">
-        <v>-6.742596466370251</v>
+        <v>-8.083137984490868</v>
       </c>
       <c r="F81">
-        <v>-3.52872931173701</v>
+        <v>-2.975627568520377</v>
       </c>
       <c r="G81">
-        <v>0.2870761163151063</v>
+        <v>-2.097483351257615</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.047406514500814</v>
       </c>
       <c r="E82">
-        <v>-7.505028464197663</v>
+        <v>-9.580604712399285</v>
       </c>
       <c r="F82">
-        <v>-3.368840320750857</v>
+        <v>-2.466744077265182</v>
       </c>
       <c r="G82">
-        <v>0.4665341689079188</v>
+        <v>-1.238823844191308</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.648118044739386</v>
       </c>
       <c r="E83">
-        <v>-9.764225276462303</v>
+        <v>-10.05492613691069</v>
       </c>
       <c r="F83">
-        <v>-3.487093080970098</v>
+        <v>-3.232932566075751</v>
       </c>
       <c r="G83">
-        <v>2.139981833554111</v>
+        <v>-0.06314318573885326</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.314386911346078</v>
       </c>
       <c r="E84">
-        <v>-9.36228245201549</v>
+        <v>-11.61674700894212</v>
       </c>
       <c r="F84">
-        <v>-3.064869245558773</v>
+        <v>-3.241291621537401</v>
       </c>
       <c r="G84">
-        <v>0.4562483039174033</v>
+        <v>-0.5414839107081471</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.067037095684743</v>
       </c>
       <c r="E85">
-        <v>-11.53078751532852</v>
+        <v>-12.00624558681585</v>
       </c>
       <c r="F85">
-        <v>-3.725274388664443</v>
+        <v>-3.243225031055535</v>
       </c>
       <c r="G85">
-        <v>1.620308947527017</v>
+        <v>0.5767885775478064</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.909266090705487</v>
       </c>
       <c r="E86">
-        <v>-13.48403156668694</v>
+        <v>-13.78614418163466</v>
       </c>
       <c r="F86">
-        <v>-3.825341999290026</v>
+        <v>-3.590198314861747</v>
       </c>
       <c r="G86">
-        <v>0.3572762344753518</v>
+        <v>0.532933780789081</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.853718558514831</v>
       </c>
       <c r="E87">
-        <v>-13.88212518822723</v>
+        <v>-14.74580027944413</v>
       </c>
       <c r="F87">
-        <v>-3.609171241855467</v>
+        <v>-3.480506731750439</v>
       </c>
       <c r="G87">
-        <v>2.39926707073537</v>
+        <v>0.4520273583548325</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.909041874567158</v>
       </c>
       <c r="E88">
-        <v>-14.70796035063603</v>
+        <v>-16.07478513189717</v>
       </c>
       <c r="F88">
-        <v>-3.95711537225776</v>
+        <v>-3.34055323068006</v>
       </c>
       <c r="G88">
-        <v>2.014737274712404</v>
+        <v>1.289661590701228</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.072463080020495</v>
       </c>
       <c r="E89">
-        <v>-17.5477573438981</v>
+        <v>-17.20847048582141</v>
       </c>
       <c r="F89">
-        <v>-4.148008498395892</v>
+        <v>-3.745724294737354</v>
       </c>
       <c r="G89">
-        <v>2.456052858370489</v>
+        <v>0.6706127486762912</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.353188402067205</v>
       </c>
       <c r="E90">
-        <v>-17.68499727717456</v>
+        <v>-17.91959487314192</v>
       </c>
       <c r="F90">
-        <v>-4.241676970834849</v>
+        <v>-3.34203849343328</v>
       </c>
       <c r="G90">
-        <v>2.118718199555373</v>
+        <v>0.8460782833487426</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.745316525076935</v>
       </c>
       <c r="E91">
-        <v>-20.28027025944445</v>
+        <v>-20.85335770206315</v>
       </c>
       <c r="F91">
-        <v>-4.256064055886671</v>
+        <v>-3.713434533376229</v>
       </c>
       <c r="G91">
-        <v>2.517698526857257</v>
+        <v>0.872817559669436</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.243472085173528</v>
       </c>
       <c r="E92">
-        <v>-21.55762597973604</v>
+        <v>-22.63353706227042</v>
       </c>
       <c r="F92">
-        <v>-3.899487508779804</v>
+        <v>-3.425649757234848</v>
       </c>
       <c r="G92">
-        <v>1.534549265332197</v>
+        <v>0.9204993470715589</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.850626356186292</v>
       </c>
       <c r="E93">
-        <v>-23.29809062289605</v>
+        <v>-24.81116700070891</v>
       </c>
       <c r="F93">
-        <v>-3.923346975082638</v>
+        <v>-3.275248058112958</v>
       </c>
       <c r="G93">
-        <v>0.9450073156987835</v>
+        <v>1.164605732955259</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.547104559307463</v>
       </c>
       <c r="E94">
-        <v>-26.45210937060235</v>
+        <v>-26.57894739908318</v>
       </c>
       <c r="F94">
-        <v>-3.710624711145933</v>
+        <v>-3.520664326703354</v>
       </c>
       <c r="G94">
-        <v>0.08290815181717369</v>
+        <v>0.8506302834652405</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.327277252260139</v>
       </c>
       <c r="E95">
-        <v>-27.78667330303284</v>
+        <v>-28.3612732559701</v>
       </c>
       <c r="F95">
-        <v>-4.103831664804595</v>
+        <v>-4.018370656592575</v>
       </c>
       <c r="G95">
-        <v>0.7295868069128681</v>
+        <v>0.04543608685816313</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.187366116823199</v>
       </c>
       <c r="E96">
-        <v>-30.67021309097199</v>
+        <v>-30.12702036951493</v>
       </c>
       <c r="F96">
-        <v>-4.760401466835302</v>
+        <v>-3.926777244497631</v>
       </c>
       <c r="G96">
-        <v>-0.2360827741648408</v>
+        <v>0.1206715447836401</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.092701536344856</v>
       </c>
       <c r="E97">
-        <v>-30.78630731486964</v>
+        <v>-33.2852755046554</v>
       </c>
       <c r="F97">
-        <v>-4.581662147231045</v>
+        <v>-4.067649405017715</v>
       </c>
       <c r="G97">
-        <v>-0.797365907075035</v>
+        <v>0.008344734636168749</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.053739638000632</v>
       </c>
       <c r="E98">
-        <v>-36.16955569809482</v>
+        <v>-35.46046912407776</v>
       </c>
       <c r="F98">
-        <v>-4.045549391078427</v>
+        <v>-4.186231027095867</v>
       </c>
       <c r="G98">
-        <v>-0.8850026685906218</v>
+        <v>-1.160969744744268</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.01996888917905</v>
       </c>
       <c r="E99">
-        <v>-36.63719535920791</v>
+        <v>-36.66244160180067</v>
       </c>
       <c r="F99">
-        <v>-4.995889752103146</v>
+        <v>-4.038444483864615</v>
       </c>
       <c r="G99">
-        <v>-0.6846153470985369</v>
+        <v>-0.3755825420986501</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.01307794062019</v>
       </c>
       <c r="E100">
-        <v>-40.02863520642535</v>
+        <v>-40.34431739373706</v>
       </c>
       <c r="F100">
-        <v>-4.413603796918483</v>
+        <v>-4.125601988517568</v>
       </c>
       <c r="G100">
-        <v>-1.506994585599971</v>
+        <v>-1.809806875531567</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.94786377157335</v>
       </c>
       <c r="E101">
-        <v>-42.99835411896748</v>
+        <v>-41.85873872833019</v>
       </c>
       <c r="F101">
-        <v>-4.734650837751877</v>
+        <v>-4.358163651751321</v>
       </c>
       <c r="G101">
-        <v>-1.330085653072397</v>
+        <v>-1.563601603775969</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.92157160999724</v>
       </c>
       <c r="E102">
-        <v>-44.88076604413492</v>
+        <v>-44.54326114058025</v>
       </c>
       <c r="F102">
-        <v>-5.122176847762138</v>
+        <v>-4.476751072401293</v>
       </c>
       <c r="G102">
-        <v>-2.325252194905012</v>
+        <v>-1.827597747259611</v>
       </c>
     </row>
   </sheetData>
